--- a/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -137,18 +121,6 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">The command could not be loaded, possibly because:
-  * You intended to execute a .NET application:
-      The application '/apps/Server/Project11.dll' does not exist.
-  * You intended to execute a .NET SDK command:
-      No .NET SDKs were found.
-Download a .NET SDK:
-https://aka.ms/dotnet/download
-Learn about SDK resolution:
-https://aka.ms/dotnet/sdk-not-found
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -209,6 +181,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -227,37 +202,10 @@
     <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
-    <x:t>ACK, PSH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, RST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, FIN</x:t>
+    <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -284,7 +232,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -293,22 +241,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -331,7 +264,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -341,17 +274,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -365,18 +289,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -810,13 +722,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -907,7 +819,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -918,13 +830,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -936,10 +848,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -977,7 +889,7 @@
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="56.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1036,7 +948,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1044,16 +956,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -1065,7 +977,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1076,16 +988,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -1097,10 +1009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1133,11 +1045,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P12"/>
+  <x:dimension ref="A1:P10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1147,7 +1059,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1159,49 +1071,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1212,7 +1124,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1221,31 +1133,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1262,40 +1174,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1312,7 +1224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1321,31 +1233,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1362,7 +1274,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1371,37 +1283,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="P5" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P5" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
@@ -1412,7 +1324,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1421,37 +1333,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>66</x:v>
+      <x:c r="P6" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1462,7 +1374,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1471,22 +1383,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1500,8 +1412,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="5" t="s">
-        <x:v>29</x:v>
+      <x:c r="P7" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1512,7 +1424,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1521,37 +1433,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>66</x:v>
+      <x:c r="P8" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1562,7 +1474,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1571,22 +1483,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1600,8 +1512,8 @@
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="5" t="s">
-        <x:v>29</x:v>
+      <x:c r="P9" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1612,7 +1524,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1621,22 +1533,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1650,108 +1562,8 @@
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="5" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="6" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:16">
-      <x:c r="A12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="6" t="s">
-        <x:v>74</x:v>
+      <x:c r="P10" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
@@ -120,7 +120,7 @@
     <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">
+    <x:t>Server is not running
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
@@ -137,15 +137,10 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">The command could not be loaded, possibly because:
-  * You intended to execute a .NET application:
-      The application '/apps/Server/Project11.dll' does not exist.
-  * You intended to execute a .NET SDK command:
-      No .NET SDKs were found.
-Download a .NET SDK:
-https://aka.ms/dotnet/download
-Learn about SDK resolution:
-https://aka.ms/dotnet/sdk-not-found
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
 </x:t>
   </x:si>
   <x:si>
@@ -239,25 +234,19 @@
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
-    <x:t>ACK, FIN</x:t>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
   </x:si>
   <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN, ACK</x:t>
-  </x:si>
-  <x:si>
     <x:t>(Not validated by this test case)</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -971,13 +960,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="56.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1079,13 +1068,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -1097,10 +1086,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="S3" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1133,7 +1122,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P12"/>
+  <x:dimension ref="A1:P11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -1159,49 +1148,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1212,7 +1201,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1221,31 +1210,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="L2" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
+      <x:c r="M2" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1262,7 +1251,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1271,31 +1260,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="J3" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
+      <x:c r="L3" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1312,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1321,31 +1310,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
+      <x:c r="L4" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1362,7 +1351,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1371,31 +1360,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
         <x:v>20</x:v>
@@ -1412,7 +1401,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1421,31 +1410,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
@@ -1462,7 +1451,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1471,22 +1460,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1512,7 +1501,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1521,37 +1510,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
+      <x:c r="L8" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="5" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="5" t="s">
-        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1562,7 +1551,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1571,22 +1560,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1612,7 +1601,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1621,37 +1610,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K10" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P10" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:16">
@@ -1686,71 +1675,21 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="6" t="s">
-        <x:v>74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:16">
-      <x:c r="A12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="6" t="s">
         <x:v>74</x:v>
       </x:c>
     </x:row>

--- a/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
@@ -120,7 +120,7 @@
     <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
-    <x:t>Server is not running
+    <x:t xml:space="preserve">
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
@@ -234,19 +234,25 @@
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
+    <x:t>ACK, FIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
     <x:t>PARTIAL</x:t>
   </x:si>
   <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
     <x:t>(Not validated by this test case)</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1122,7 +1128,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P11"/>
+  <x:dimension ref="A1:P12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -1525,10 +1531,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
         <x:v>59</x:v>
@@ -1540,7 +1546,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1560,10 +1566,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1625,22 +1631,22 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P10" s="5" t="s">
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:16">
@@ -1648,7 +1654,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>17</x:v>
@@ -1690,7 +1696,57 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="6" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:16">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>74</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="6" t="s">
+        <x:v>75</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
@@ -120,7 +120,7 @@
     <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">
+    <x:t>Server is not running
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
@@ -225,34 +225,25 @@
     <x:t>ACK, PSH</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>ACK, RST</x:t>
   </x:si>
   <x:si>
     <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, FIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -279,7 +270,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -294,11 +285,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -326,7 +312,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -342,11 +328,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -368,10 +351,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1128,7 +1107,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P12"/>
+  <x:dimension ref="A1:P13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -1431,10 +1410,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
         <x:v>59</x:v>
@@ -1481,7 +1460,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1531,22 +1510,22 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="5" t="s">
-        <x:v>72</x:v>
+      <x:c r="P8" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1566,10 +1545,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1581,7 +1560,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1631,22 +1610,22 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="5" t="s">
-        <x:v>72</x:v>
+      <x:c r="P10" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:16">
@@ -1654,7 +1633,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>17</x:v>
@@ -1695,8 +1674,8 @@
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P11" s="6" t="s">
-        <x:v>75</x:v>
+      <x:c r="P11" s="5" t="s">
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
@@ -1704,7 +1683,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>17</x:v>
@@ -1731,10 +1710,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
         <x:v>59</x:v>
@@ -1745,8 +1724,58 @@
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="6" t="s">
-        <x:v>75</x:v>
+      <x:c r="P12" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:16">
+      <x:c r="A13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P13" s="5" t="s">
+        <x:v>71</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server is not running
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -137,13 +121,6 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Waiting for a connection from client
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -204,6 +181,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -222,28 +202,10 @@
     <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
-    <x:t>ACK, PSH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, RST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -270,7 +232,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -279,17 +241,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -312,7 +264,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -322,14 +274,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -343,14 +289,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -784,13 +722,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -881,7 +819,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -892,13 +830,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -910,10 +848,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -945,13 +883,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1010,7 +948,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1018,16 +956,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -1039,7 +977,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1050,7 +988,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1071,10 +1009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1107,11 +1045,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P13"/>
+  <x:dimension ref="A1:P10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1121,7 +1059,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1133,49 +1071,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1186,7 +1124,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1195,31 +1133,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1236,40 +1174,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1286,7 +1224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1295,31 +1233,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1336,7 +1274,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1345,34 +1283,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1386,7 +1324,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1395,31 +1333,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
@@ -1436,7 +1374,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1445,22 +1383,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1474,8 +1412,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P7" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1486,7 +1424,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1495,22 +1433,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1524,8 +1462,8 @@
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P8" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1536,7 +1474,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1545,22 +1483,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1574,8 +1512,8 @@
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P9" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1586,7 +1524,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1595,22 +1533,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1624,158 +1562,8 @@
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="5" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:16">
-      <x:c r="A12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="5" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:16">
-      <x:c r="A13" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="M13" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P13" s="5" t="s">
-        <x:v>71</x:v>
+      <x:c r="P10" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
@@ -92,22 +92,38 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: client output matches exactly</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+Enter operation (format as A X B):</x:t>
+  </x:si>
+  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -121,6 +137,13 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -181,31 +204,49 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>SYN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server responding (SYN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection established</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSH, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data transfer in progress</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server responding (SYN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection established</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSH, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection reset (RST) - Error occurred</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -232,7 +273,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -241,7 +282,22 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF00"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -264,7 +320,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -274,8 +330,17 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -289,6 +354,18 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -722,13 +799,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -819,7 +896,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -830,13 +907,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -848,10 +925,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -883,13 +960,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -948,7 +1025,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -956,16 +1033,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -977,7 +1054,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -988,7 +1065,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1009,10 +1086,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1045,11 +1122,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P10"/>
+  <x:dimension ref="A1:P13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1059,7 +1136,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1071,49 +1148,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1124,7 +1201,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1133,31 +1210,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1174,7 +1251,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1183,31 +1260,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1224,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1233,31 +1310,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1274,7 +1351,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1283,34 +1360,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="J5" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1324,7 +1401,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1333,22 +1410,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1362,8 +1439,8 @@
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P6" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1374,7 +1451,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1383,22 +1460,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1412,8 +1489,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P7" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1424,7 +1501,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1433,22 +1510,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1462,8 +1539,8 @@
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P8" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1474,7 +1551,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1483,37 +1560,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P9" s="5" t="s">
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1524,7 +1601,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1533,37 +1610,187 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P10" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:16">
+      <x:c r="A11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G10" s="0" t="s">
+      <x:c r="L11" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="M11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="6" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:16">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="6" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:16">
+      <x:c r="A13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P13" s="6" t="s">
+        <x:v>71</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -137,13 +121,6 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Waiting for a connection from client
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -204,6 +181,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -222,31 +202,10 @@
     <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -273,7 +232,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -282,22 +241,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -320,7 +264,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -330,17 +274,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -354,18 +289,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -799,13 +722,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -896,7 +819,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -907,13 +830,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -925,10 +848,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -960,13 +883,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1025,7 +948,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1033,16 +956,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -1054,7 +977,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1065,7 +988,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1086,10 +1009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1122,11 +1045,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P13"/>
+  <x:dimension ref="A1:P10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1136,7 +1059,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1148,49 +1071,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1201,7 +1124,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1210,31 +1133,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1251,40 +1174,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1301,7 +1224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1310,31 +1233,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1351,7 +1274,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1360,34 +1283,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1401,7 +1324,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1410,22 +1333,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1439,8 +1362,8 @@
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P6" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1451,7 +1374,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1460,22 +1383,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1489,8 +1412,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P7" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1501,7 +1424,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1510,22 +1433,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1539,8 +1462,8 @@
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P8" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1551,7 +1474,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1560,37 +1483,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="5" t="s">
-        <x:v>69</x:v>
+      <x:c r="P9" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1601,7 +1524,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1610,22 +1533,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1639,158 +1562,8 @@
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="6" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:16">
-      <x:c r="A12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="6" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:16">
-      <x:c r="A13" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="M13" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P13" s="6" t="s">
-        <x:v>71</x:v>
+      <x:c r="P10" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
@@ -92,22 +92,38 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: client output matches exactly</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+Enter operation (format as A X B):</x:t>
+  </x:si>
+  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -119,6 +135,13 @@
   </x:si>
   <x:si>
     <x:t>Waiting for a connection from client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
+</x:t>
   </x:si>
   <x:si>
     <x:t>Time</x:t>
@@ -722,13 +745,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -819,7 +842,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -830,13 +853,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -848,10 +871,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -883,13 +906,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -948,7 +971,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -956,16 +979,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -977,7 +1000,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -988,7 +1011,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1009,10 +1032,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1071,49 +1094,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1124,7 +1147,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1133,22 +1156,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
         <x:v>17</x:v>
@@ -1163,7 +1186,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16">
@@ -1174,7 +1197,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1183,22 +1206,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1213,7 +1236,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16">
@@ -1224,7 +1247,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1233,22 +1256,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>17</x:v>
@@ -1263,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:16">
@@ -1274,7 +1297,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1283,22 +1306,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="J5" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>17</x:v>
@@ -1313,7 +1336,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
@@ -1324,7 +1347,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1333,22 +1356,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1363,7 +1386,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1374,7 +1397,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1383,22 +1406,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1413,7 +1436,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1424,7 +1447,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1433,22 +1456,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1463,7 +1486,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1474,7 +1497,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1483,23 +1506,23 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1513,7 +1536,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1524,7 +1547,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1533,22 +1556,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1563,7 +1586,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -135,13 +119,6 @@
   </x:si>
   <x:si>
     <x:t>Waiting for a connection from client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Waiting for a connection from client
-</x:t>
   </x:si>
   <x:si>
     <x:t>Time</x:t>
@@ -745,13 +722,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -842,7 +819,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -853,13 +830,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -871,10 +848,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -906,13 +883,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -971,7 +948,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -979,16 +956,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -1000,7 +977,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1011,7 +988,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1032,10 +1009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1094,49 +1071,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1147,7 +1124,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1156,22 +1133,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
         <x:v>17</x:v>
@@ -1186,7 +1163,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16">
@@ -1197,31 +1174,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1236,7 +1213,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16">
@@ -1247,7 +1224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1256,22 +1233,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>17</x:v>
@@ -1286,7 +1263,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:16">
@@ -1297,7 +1274,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1306,22 +1283,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>17</x:v>
@@ -1336,7 +1313,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
@@ -1347,7 +1324,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1356,22 +1333,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1386,7 +1363,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1397,7 +1374,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1406,22 +1383,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1436,7 +1413,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1447,7 +1424,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1456,22 +1433,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1486,7 +1463,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1497,7 +1474,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1506,22 +1483,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1536,7 +1513,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1547,7 +1524,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1556,22 +1533,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1586,7 +1563,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
@@ -92,16 +92,16 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: client output matches exactly</x:t>
   </x:si>
   <x:si>
     <x:t>3
@@ -115,12 +115,29 @@
 Client disconnected</x:t>
   </x:si>
   <x:si>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
     <x:t>Text comparison failed: server output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Unhandled exception. System.Net.Sockets.SocketException (98): Address already in use
+   at System.Net.Sockets.Socket.DoBind(EndPoint endPointSnapshot, SocketAddress socketAddress)
+   at System.Net.Sockets.Socket.Bind(EndPoint localEP)
+   at System.Net.Sockets.TcpListener.Start(Int32 backlog)
+   at Program.&lt;Main&gt;$(String[] args)
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -181,9 +198,6 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -202,10 +216,22 @@
     <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -232,7 +258,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -241,7 +267,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF00"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -264,7 +300,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -274,8 +310,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -289,6 +331,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -716,19 +766,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -819,7 +869,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -850,8 +900,8 @@
       <x:c r="M3" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="S3" s="2" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -889,7 +939,7 @@
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="91.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -959,13 +1009,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -977,7 +1027,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -988,16 +1038,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -1009,10 +1059,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1045,11 +1095,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P10"/>
+  <x:dimension ref="A1:P19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1058,8 +1108,8 @@
     <x:col min="8" max="8" width="4.996339" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1071,49 +1121,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1124,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1133,31 +1183,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1174,7 +1224,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1183,31 +1233,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1224,7 +1274,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1233,31 +1283,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1274,7 +1324,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1283,34 +1333,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1324,7 +1374,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1333,37 +1383,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P6" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1374,7 +1424,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1383,37 +1433,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P7" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1424,7 +1474,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1433,37 +1483,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P8" s="4" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1474,7 +1524,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1483,31 +1533,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
@@ -1524,7 +1574,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1533,37 +1583,487 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
         <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:16">
+      <x:c r="A11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="5" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:16">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="5" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:16">
+      <x:c r="A13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="P13" s="5" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:16">
+      <x:c r="A14" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P14" s="5" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:16">
+      <x:c r="A15" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="P15" s="5" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:16">
+      <x:c r="A16" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M16" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="O16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P16" s="5" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:16">
+      <x:c r="A17" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M17" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P17" s="5" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:16">
+      <x:c r="A18" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M18" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P18" s="5" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:16">
+      <x:c r="A19" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L19" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M19" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P19" s="5" t="s">
+        <x:v>67</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC4_Full/GradeDetail.xlsx
@@ -115,26 +115,18 @@
 Client disconnected</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: server output mismatch</x:t>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Client connected
+Client disconnected
+</x:t>
   </x:si>
   <x:si>
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Unhandled exception. System.Net.Sockets.SocketException (98): Address already in use
-   at System.Net.Sockets.Socket.DoBind(EndPoint endPointSnapshot, SocketAddress socketAddress)
-   at System.Net.Sockets.Socket.Bind(EndPoint localEP)
-   at System.Net.Sockets.TcpListener.Start(Int32 backlog)
-   at Program.&lt;Main&gt;$(String[] args)
+    <x:t xml:space="preserve">Waiting for a connection from client
 </x:t>
   </x:si>
   <x:si>
@@ -927,19 +919,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="91.282054" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1009,13 +1001,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -1027,10 +1019,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S2" s="2" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -1038,16 +1030,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -1059,10 +1051,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>36</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1121,49 +1113,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="E1" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="F1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="G1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="L1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="M1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="N1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1174,40 +1166,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1224,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1233,31 +1225,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1274,7 +1266,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1283,31 +1275,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1324,7 +1316,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1333,31 +1325,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
         <x:v>20</x:v>
@@ -1374,7 +1366,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1383,37 +1375,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1424,7 +1416,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1433,37 +1425,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="P7" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1474,7 +1466,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1483,37 +1475,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1524,7 +1516,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
@@ -1533,31 +1525,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
@@ -1574,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>17</x:v>
@@ -1583,31 +1575,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
@@ -1621,7 +1613,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>17</x:v>
@@ -1648,22 +1640,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:16">
@@ -1671,7 +1663,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>17</x:v>
@@ -1698,22 +1690,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P12" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:16">
@@ -1721,49 +1713,49 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J13" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K13" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L13" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="M13" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="N13" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="O13" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="P13" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:16">
@@ -1771,7 +1763,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>17</x:v>
@@ -1798,22 +1790,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L14" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M14" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N14" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O14" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P14" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:16">
@@ -1821,49 +1813,49 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J15" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K15" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L15" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="M15" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="N15" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="O15" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="P15" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:16">
@@ -1871,7 +1863,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>17</x:v>
@@ -1898,22 +1890,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M16" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N16" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O16" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P16" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -1921,7 +1913,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>17</x:v>
@@ -1948,22 +1940,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M17" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P17" s="5" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="M17" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="N17" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="O17" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P17" s="5" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -1971,7 +1963,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>17</x:v>
@@ -1998,22 +1990,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M18" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N18" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O18" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P18" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
@@ -2021,7 +2013,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>17</x:v>
@@ -2048,22 +2040,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M19" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N19" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O19" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
